--- a/Scottish MOD3_SOL-Design and timings.xlsx
+++ b/Scottish MOD3_SOL-Design and timings.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QA\Scotland\2025 Scotland Level 8 courses\Mod-3 Designing Software\Mike B New version\The new course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4465052-5A36-450C-88A3-F1154CE16A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02520E56-672C-46DB-ACC0-1D78C4C660A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KSPs &amp; Design" sheetId="2" r:id="rId1"/>
     <sheet name="Timing" sheetId="1" r:id="rId2"/>
-    <sheet name="Teaching Tips" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="54">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -106,15 +105,6 @@
     <t>Read the Scenario and gather requirement</t>
   </si>
   <si>
-    <t>Lab 2.1-Write User stories.docx</t>
-  </si>
-  <si>
-    <t>2-Agile and User Stories.pptx</t>
-  </si>
-  <si>
-    <t>Lab 2.2 - Backlog + Prioritisation.docx</t>
-  </si>
-  <si>
     <t>Lab 2.3 Sprint Planning.docx</t>
   </si>
   <si>
@@ -146,9 +136,6 @@
   </si>
   <si>
     <t>Design:</t>
-  </si>
-  <si>
-    <t>Critical teaching tips</t>
   </si>
   <si>
     <t>1. Keep explanations short</t>
@@ -206,6 +193,12 @@
   </si>
   <si>
     <t>8-Review and Improvement.pptx</t>
+  </si>
+  <si>
+    <t>🔚</t>
+  </si>
+  <si>
+    <t>Teaching tips</t>
   </si>
 </sst>
 </file>
@@ -283,7 +276,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,8 +313,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4E4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -329,11 +328,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -372,9 +408,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -390,9 +423,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -411,13 +441,25 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,6 +468,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEAF4E4"/>
       <color rgb="FFF2F8EE"/>
     </mruColors>
   </colors>
@@ -4580,116 +4623,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="34" t="s">
-        <v>34</v>
+      <c r="A1" s="32" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="25"/>
+      <c r="A2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="25"/>
+      <c r="A3" s="24"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
+      <c r="A4" s="26"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
+      <c r="A5" s="26"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
+      <c r="A6" s="26"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
+      <c r="A7" s="25"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
+      <c r="A8" s="26"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
+      <c r="A9" s="26"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-    </row>
-    <row r="12" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
-    </row>
-    <row r="13" spans="1:3" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+    </row>
+    <row r="12" spans="1:3" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+    </row>
+    <row r="13" spans="1:3" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="29"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
+      <c r="A14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
+      <c r="A15" s="27"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
+      <c r="A16" s="26"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
+      <c r="A17" s="26"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="26"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+      <c r="A19" s="26"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+      <c r="A20" s="26"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+      <c r="A21" s="26"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+      <c r="A22" s="26"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="26"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="26"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="26"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
+      <c r="A26" s="26"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
+      <c r="A27" s="26"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
+      <c r="A28" s="26"/>
     </row>
     <row r="29" spans="1:1" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="29"/>
+      <c r="A29" s="27"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
+      <c r="A30" s="25"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30"/>
+      <c r="A31" s="28"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30"/>
+      <c r="A32" s="28"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30"/>
+      <c r="A33" s="28"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30"/>
+      <c r="A34" s="28"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="26"/>
+      <c r="A35" s="25"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
+      <c r="A36" s="25"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="18"/>
@@ -4698,8 +4741,8 @@
       <c r="A38" s="18"/>
     </row>
     <row r="45" spans="1:1" ht="36.6" x14ac:dyDescent="0.7">
-      <c r="A45" s="33" t="s">
-        <v>35</v>
+      <c r="A45" s="31" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4710,7 +4753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -4719,11 +4762,12 @@
     <col min="4" max="4" width="16.88671875" customWidth="1"/>
     <col min="5" max="5" width="32.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="57.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="10"/>
       <c r="B1" s="9"/>
       <c r="C1" s="11"/>
@@ -4732,7 +4776,7 @@
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4749,9 +4793,9 @@
         <v>11</v>
       </c>
       <c r="F2" s="17"/>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -4770,11 +4814,11 @@
       <c r="F3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="34" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -4785,15 +4829,16 @@
       <c r="C4" s="5">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="36"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" s="19"/>
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" spans="1:11" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -4813,9 +4858,12 @@
       <c r="F5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="36"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="34"/>
+      <c r="I5" s="35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -4833,9 +4881,12 @@
         <v>6</v>
       </c>
       <c r="F6" s="19"/>
-      <c r="G6" s="36"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="34"/>
+      <c r="I6" s="36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -4855,9 +4906,12 @@
       <c r="F7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="36"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="34"/>
+      <c r="I7" s="37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -4874,9 +4928,13 @@
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="36"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="19"/>
+      <c r="G8" s="34"/>
+      <c r="I8" s="37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="1">
         <f>B8+ TIME(0, C8, 0)</f>
@@ -4889,11 +4947,12 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="36"/>
-    </row>
-    <row r="10" spans="1:7" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="G9" s="34"/>
+      <c r="I9" s="36"/>
+    </row>
+    <row r="10" spans="1:11" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>1</v>
       </c>
@@ -4907,13 +4966,19 @@
       <c r="D10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="36"/>
-    </row>
-    <row r="11" spans="1:7" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="34"/>
+      <c r="H10"/>
+      <c r="I10" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:11" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1</v>
       </c>
@@ -4930,10 +4995,16 @@
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="36"/>
-    </row>
-    <row r="12" spans="1:7" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="19"/>
+      <c r="G11" s="34"/>
+      <c r="H11"/>
+      <c r="I11" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:11" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>1</v>
       </c>
@@ -4947,13 +5018,19 @@
       <c r="D12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="36"/>
-    </row>
-    <row r="13" spans="1:7" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="34"/>
+      <c r="H12"/>
+      <c r="I12" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:11" s="15" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>1</v>
       </c>
@@ -4964,16 +5041,20 @@
       <c r="C13" s="13">
         <v>40</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="36"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="34"/>
+      <c r="H13"/>
+      <c r="I13" s="36"/>
+      <c r="J13"/>
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -4988,11 +5069,14 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="36"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="G14" s="34"/>
+      <c r="I14" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>1</v>
       </c>
@@ -5006,22 +5090,34 @@
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="F15" s="19"/>
-      <c r="G15" s="36"/>
-    </row>
-    <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G16" s="36"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="34"/>
+      <c r="I15" s="37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="34"/>
+      <c r="I16" s="38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="9"/>
       <c r="D17" s="11"/>
       <c r="E17" s="12"/>
-      <c r="F17" s="21"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17" s="38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>0</v>
       </c>
@@ -5038,9 +5134,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="17"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="21"/>
+      <c r="I18" s="36"/>
+    </row>
+    <row r="19" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>2</v>
       </c>
@@ -5054,13 +5151,16 @@
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="34" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>2</v>
       </c>
@@ -5075,11 +5175,14 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="G20" s="34"/>
+      <c r="I20" s="39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2</v>
       </c>
@@ -5090,12 +5193,14 @@
       <c r="C21" s="5">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="36"/>
-    </row>
-    <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="2"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="34"/>
+    </row>
+    <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2</v>
       </c>
@@ -5110,11 +5215,11 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="G22" s="34"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2</v>
       </c>
@@ -5131,9 +5236,10 @@
       <c r="E23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="36"/>
-    </row>
-    <row r="24" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="19"/>
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>2</v>
       </c>
@@ -5148,11 +5254,11 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="36"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="G24" s="34"/>
+    </row>
+    <row r="25" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2</v>
       </c>
@@ -5163,15 +5269,16 @@
       <c r="C25" s="5">
         <v>30</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="34"/>
+    </row>
+    <row r="26" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>2</v>
       </c>
@@ -5188,9 +5295,10 @@
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="36"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="19"/>
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>2</v>
       </c>
@@ -5205,11 +5313,11 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="36"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -5220,36 +5328,37 @@
       <c r="C28" s="5">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="36"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="19"/>
+      <c r="G28" s="34"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="1"/>
       <c r="C29" s="5"/>
       <c r="D29" s="3"/>
-      <c r="G29" s="36"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="34"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="10"/>
       <c r="C30" s="9"/>
       <c r="D30" s="11"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F30" s="20"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F31"/>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="B32" s="37" t="s">
-        <v>49</v>
+    <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="B32" s="33" t="s">
+        <v>45</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -5258,7 +5367,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -5274,7 +5383,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -5283,7 +5392,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -5292,7 +5401,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5301,7 +5410,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -5317,7 +5426,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5504,94 +5613,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06857BD6-C74E-4F29-965A-A30D6CA75220}">
-  <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>